--- a/ig/DM-JUILLET-2025/CodeSystem-TRE-R356-ProfessionRessource.xlsx
+++ b/ig/DM-JUILLET-2025/CodeSystem-TRE-R356-ProfessionRessource.xlsx
@@ -118,475 +118,475 @@
     <t>Count</t>
   </si>
   <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>dateValid</t>
+  </si>
+  <si>
+    <t>date de validité d'un code concept</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>dateMaj</t>
+  </si>
+  <si>
+    <t>Date de mise à jour d'un code concept</t>
+  </si>
+  <si>
+    <t>dateFin</t>
+  </si>
+  <si>
+    <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date Concept was deprecated</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A property that indicates the status of the concept.</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date Concept was retired</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Art-thérapeute</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>Neuropsychologue</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>Médiateur de santé pair</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Socio-esthéticien</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Enseignant du 1er degré</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Enseignant du 2nd degré</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Enseignant du supérieur</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Puériculteur</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Aide humaine en milieu scolaire</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Médecin coordonnateur</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Infirmier coordonnateur</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Phoniatre</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Audio phonologue</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Ingénieur en analyse du mouvement</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Psychologue clinicien</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Animateur socio-culturel</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Moniteur d'atelier</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Enseignant en Activité Physique Adaptée (EAPA)</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Accompagnant des Élèves en Situation de Handicap (AESH)</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Pédopsychiatre</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Veilleur de nuit</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Assistant de soins en gérontologie</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>Aide médico psychologique (AMP)</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Avéjiste</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>Instructeur en locomotion</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>Educateur sportif</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>Conseiller en insertion professionnelle</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Coordonnateur et gestionnaire de parcours handicap</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Neuropédiatre</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>Psychopédagogue</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>Tabacologue</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Addictologue</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>Allergologue</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>Cardiologue</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>Chercheur médical</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>Chirurgien digestif</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>Chirurgien général</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>Chirurgien maxillo-facial</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>Chirurgien oral</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>Chirurgien orthopédiste</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>Chirurgien pédiatrique</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>Chirurgien plastique, plasticien</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>Chirurgien thoracique et cardiaque</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>Chirurgien urologue</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>Chirurgien vasculaire</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>Dentiste</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>Dermatologue</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>Endocrinologue</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>Gastro-entérologue</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Généticien médicale</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>Gériatre</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>Gynécologue</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>Gynéco-obstétricien</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>Hématologue</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>Infectiologue</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>Infirmier en pratique avancée (IPA)</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>Médecin anesthésiste-réanimateur</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>Médecin généraliste</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>Médecin interniste</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>Médecin légiste</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>Médecin nucléaire</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>Médecin rééducateur</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>Médecin vasculaire</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>Néphrologue</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>Neurochirurgien</t>
+  </si>
+  <si>
     <t>98</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Uri</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>dateValid</t>
-  </si>
-  <si>
-    <t>date de validité d'un code concept</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>dateMaj</t>
-  </si>
-  <si>
-    <t>Date de mise à jour d'un code concept</t>
-  </si>
-  <si>
-    <t>dateFin</t>
-  </si>
-  <si>
-    <t>Date de fin d'exploitation d'un code concept</t>
-  </si>
-  <si>
-    <t>deprecationDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
-  </si>
-  <si>
-    <t>Date Concept was deprecated</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A property that indicates the status of the concept.</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>retirementDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
-  </si>
-  <si>
-    <t>Date Concept was retired</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>Art-thérapeute</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>Neuropsychologue</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>Médiateur de santé pair</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Socio-esthéticien</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Enseignant du 1er degré</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Enseignant du 2nd degré</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Enseignant du supérieur</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Puériculteur</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Aide humaine en milieu scolaire</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Médecin coordonnateur</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>Infirmier coordonnateur</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>Phoniatre</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>Audio phonologue</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Ingénieur en analyse du mouvement</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>Psychologue clinicien</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>Animateur socio-culturel</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Moniteur d'atelier</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>Enseignant en Activité Physique Adaptée (EAPA)</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>Accompagnant des Élèves en Situation de Handicap (AESH)</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>Pédopsychiatre</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>Veilleur de nuit</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>Assistant de soins en gérontologie</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>Aide médico psychologique (AMP)</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>Avéjiste</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>Instructeur en locomotion</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>Educateur sportif</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>Conseiller en insertion professionnelle</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>Coordonnateur et gestionnaire de parcours handicap</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>Neuropédiatre</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>Psychopédagogue</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>Tabacologue</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>Addictologue</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>Allergologue</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>Cardiologue</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>Chercheur médical</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>Chirurgien digestif</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>Chirurgien général</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>Chirurgien maxillo-facial</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>Chirurgien oral</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>Chirurgien orthopédiste</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>Chirurgien pédiatrique</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>Chirurgien plastique, plasticien</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>Chirurgien thoracique et cardiaque</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>Chirurgien urologue</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>Chirurgien vasculaire</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>Dentiste</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>Dermatologue</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>Endocrinologue</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>Gastro-entérologue</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>Généticien médicale</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>Gériatre</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>Gynécologue</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>Gynéco-obstétricien</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>Hématologue</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>Infectiologue</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>Infirmier en pratique avancée (IPA)</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>Médecin anesthésiste-réanimateur</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>Médecin généraliste</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>Médecin interniste</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>Médecin légiste</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>Médecin nucléaire</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>Médecin rééducateur</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>Médecin vasculaire</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>Néphrologue</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>Neurochirurgien</t>
-  </si>
-  <si>
     <t>Neurologue</t>
-  </si>
-  <si>
-    <t>99</t>
   </si>
   <si>
     <t>Neuro-psychiatre</t>
@@ -1990,10 +1990,10 @@
         <v>58</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>34</v>
+        <v>189</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D67" s="2"/>
     </row>
@@ -2002,7 +2002,7 @@
         <v>58</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>190</v>
+        <v>34</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>191</v>
